--- a/Financial Analysis/Models Retired.xlsx
+++ b/Financial Analysis/Models Retired.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFA3618-288C-4D9E-B88C-0E98D06A8AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DF000C-07C9-4FA9-98C0-E109DE4A2440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{86C707C2-4719-4344-B4E8-DD417FC47327}"/>
   </bookViews>
@@ -26,6 +26,9 @@
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>Alteryx</t>
   </si>
@@ -93,9 +96,6 @@
     <t>Acquired</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Quixant</t>
   </si>
   <si>
@@ -127,13 +127,28 @@
   </si>
   <si>
     <t>Merged</t>
+  </si>
+  <si>
+    <t>Farfetch</t>
+  </si>
+  <si>
+    <t>FTCH US</t>
+  </si>
+  <si>
+    <t>E-commerce</t>
+  </si>
+  <si>
+    <t>MicroAlgo</t>
+  </si>
+  <si>
+    <t>MLGO US</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0\x"/>
     <numFmt numFmtId="166" formatCode="[$$-409]#,##0"/>
@@ -142,8 +157,9 @@
     <numFmt numFmtId="169" formatCode="#,##0\ [$€-1]"/>
     <numFmt numFmtId="170" formatCode="&quot;£&quot;#,##0"/>
     <numFmt numFmtId="171" formatCode="#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="172" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +185,14 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -203,7 +227,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -241,25 +265,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -388,6 +402,176 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>37.11</v>
+          </cell>
+          <cell r="E3">
+            <v>44330</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>August?</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>13177.761</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-2054.2000000000007</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>15231.961000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="23">
+          <cell r="AO23">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AO29">
+            <v>-0.17579359601320499</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AO30" t="str">
+            <v>Slightly overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>4.4400000000000004</v>
+          </cell>
+          <cell r="E3">
+            <v>45780</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>?</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>43.067999999999998</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10">
+            <v>140.4951856946355</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="D11">
+            <v>-97.427185694635497</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="5">
+          <cell r="O5">
+            <v>334.37624999999997</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="O23">
+            <v>-65.195625000000021</v>
+          </cell>
+          <cell r="P23">
+            <v>-75.811683750000014</v>
+          </cell>
+          <cell r="Q23">
+            <v>-85.133768362500035</v>
+          </cell>
+          <cell r="R23">
+            <v>-92.999013768375065</v>
+          </cell>
+          <cell r="S23">
+            <v>-99.507942011156317</v>
+          </cell>
+          <cell r="Z23">
+            <v>-121.34020466225257</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="N27">
+            <v>-5.0000000000000044E-2</v>
+          </cell>
+          <cell r="O27">
+            <v>-0.35</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AA30">
+            <v>0.15</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="AA37">
+            <v>0.42025776126590375</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="AA38" t="str">
+            <v>Undervalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Models"/>
+      <sheetName val="Charts"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1203,16 +1387,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD31E83-7C03-4724-9D03-D6D9BD345CC1}">
-  <dimension ref="A2:AG14"/>
+  <dimension ref="A2:AH13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="20" width="9" bestFit="1" customWidth="1"/>
     <col min="22" max="26" width="9" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1283,7 +1467,7 @@
         <v>44412</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1354,7 +1538,7 @@
         <v>August?</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1422,7 +1606,7 @@
         <v>44371</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1490,7 +1674,7 @@
         <v>44406</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1558,7 +1742,7 @@
         <v>44393</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1629,15 +1813,15 @@
         <v>August?</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="D8" s="9">
         <f>[7]Main!$D$3</f>
@@ -1684,7 +1868,7 @@
         <v>Fairly valued</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB8" s="7">
         <v>2005</v>
@@ -1698,12 +1882,12 @@
         <v>August?</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D9" s="9">
         <f>[8]Main!$D$3</f>
@@ -1750,7 +1934,7 @@
         <v>Heavily undervalued</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB9" s="7">
         <v>1937</v>
@@ -1764,15 +1948,15 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="D10" s="2">
         <f>[9]Main!$D$3</f>
@@ -1879,74 +2063,246 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="11" spans="1:33" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="17" t="s">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="19">
+      <c r="D11" s="16">
         <f>[10]Main!$D$3</f>
         <v>11.16</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="3">
         <f>[10]Main!$D$5</f>
         <v>22056.624</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="3">
         <f>[10]Main!$D$8</f>
         <v>-4300</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="3">
         <f>[10]Main!$D$9</f>
         <v>26356.624</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6">
         <f>[10]Model!$S$21</f>
         <v>0.06</v>
       </c>
-      <c r="Z11" s="23">
+      <c r="Z11" s="6">
         <f>[10]Model!$S$27</f>
         <v>6.187107975628825E-3</v>
       </c>
-      <c r="AA11" s="23" t="str">
+      <c r="AA11" s="6" t="str">
         <f>[10]Model!$S$28</f>
         <v>Fairly valued</v>
       </c>
-      <c r="AB11" s="18">
+      <c r="AB11" s="7">
         <v>1899</v>
       </c>
-      <c r="AD11" s="18"/>
-      <c r="AE11" s="18"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2">
+        <f>[11]Main!$D$3</f>
+        <v>37.11</v>
+      </c>
+      <c r="E12" s="3">
+        <f>[11]Main!$D$5</f>
+        <v>13177.761</v>
+      </c>
+      <c r="F12" s="3">
+        <f>[11]Main!$D$8</f>
+        <v>-2054.2000000000007</v>
+      </c>
+      <c r="G12" s="3">
+        <f>[11]Main!$D$9</f>
+        <v>15231.961000000001</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6">
+        <f>[11]Model!$AO$23</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AB12" s="6">
+        <f>[11]Model!$AO$29</f>
+        <v>-0.17579359601320499</v>
+      </c>
+      <c r="AC12" s="7" t="str">
+        <f>[11]Model!$AO$30</f>
+        <v>Slightly overvalued</v>
+      </c>
+      <c r="AD12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE12" s="7">
+        <v>2007</v>
+      </c>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="8">
+        <f>[11]Main!$E$3</f>
+        <v>44330</v>
+      </c>
+      <c r="AH12" s="8" t="str">
+        <f>[11]Main!$G$3</f>
+        <v>August?</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C14" s="15"/>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="B13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2">
+        <f>[12]Main!$D$3</f>
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="E13" s="3">
+        <f>[12]Main!$D$5</f>
+        <v>43.067999999999998</v>
+      </c>
+      <c r="F13" s="3">
+        <f>[12]Main!$D$10</f>
+        <v>140.4951856946355</v>
+      </c>
+      <c r="G13" s="3">
+        <f>[12]Main!$D$11</f>
+        <v>-97.427185694635497</v>
+      </c>
+      <c r="H13" s="3">
+        <f>[12]Model!O$23</f>
+        <v>-65.195625000000021</v>
+      </c>
+      <c r="I13" s="3">
+        <f>[12]Model!P$23</f>
+        <v>-75.811683750000014</v>
+      </c>
+      <c r="J13" s="3">
+        <f>[12]Model!Q$23</f>
+        <v>-85.133768362500035</v>
+      </c>
+      <c r="K13" s="3">
+        <f>[12]Model!R$23</f>
+        <v>-92.999013768375065</v>
+      </c>
+      <c r="L13" s="3">
+        <f>[12]Model!S$23</f>
+        <v>-99.507942011156317</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4">
+        <f>[13]Models!$E$3/J13</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="4">
+        <f>[13]Models!$E$3/K13</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
+        <f>[13]Models!$E$3/L13</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
+        <f>E13/[12]Model!$Z$23</f>
+        <v>-0.35493594328342115</v>
+      </c>
+      <c r="S13" s="18">
+        <f>[12]Model!$O$5</f>
+        <v>334.37624999999997</v>
+      </c>
+      <c r="T13" s="19">
+        <f>G13/S13</f>
+        <v>-0.29136993340476636</v>
+      </c>
+      <c r="U13" s="6">
+        <f>[12]Model!N$27</f>
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="V13" s="6">
+        <f>[12]Model!O$27</f>
+        <v>-0.35</v>
+      </c>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6">
+        <f>[12]Model!$AA$30</f>
+        <v>0.15</v>
+      </c>
+      <c r="AA13" s="6">
+        <f>[12]Model!$AA$37</f>
+        <v>0.42025776126590375</v>
+      </c>
+      <c r="AB13" s="7" t="str">
+        <f>[12]Model!$AA$38</f>
+        <v>Undervalued</v>
+      </c>
+      <c r="AC13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="7">
+        <v>2018</v>
+      </c>
+      <c r="AF13" s="8">
+        <f>[12]Main!$E$3</f>
+        <v>45780</v>
+      </c>
+      <c r="AG13" s="8" t="str">
+        <f>[12]Main!$G$3</f>
+        <v>?</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1960,6 +2316,8 @@
     <hyperlink ref="B9" r:id="rId8" xr:uid="{7DF44C0B-FEF9-4419-BE7D-A1518B12904B}"/>
     <hyperlink ref="B10" r:id="rId9" xr:uid="{1BF4E433-5E84-4928-9E41-C67D528C31A8}"/>
     <hyperlink ref="B11" r:id="rId10" xr:uid="{4969CAB0-38DA-40ED-BFC0-6D88917C84F3}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{02B8B2FE-E563-4E55-837B-F38C68D7B6B0}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{07F19DBC-BFAA-4283-98BA-6532BD7B5211}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
